--- a/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
+++ b/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE37BB3-9088-4AE1-9F7D-12304642D1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E7B5BC-5747-4B36-AE78-D71897533EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="污染" sheetId="3" r:id="rId1"/>
     <sheet name="机械" sheetId="4" r:id="rId2"/>
     <sheet name="梦境之种" sheetId="5" r:id="rId3"/>
     <sheet name="通用" sheetId="6" r:id="rId4"/>
+    <sheet name="道具" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="132">
   <si>
     <t>序号</t>
   </si>
@@ -105,9 +106,6 @@
     <t>向右</t>
   </si>
   <si>
-    <t>被撞：+2分，自身+1污染</t>
-  </si>
-  <si>
     <t>最基本的本体叠加污染手段</t>
   </si>
   <si>
@@ -147,9 +145,6 @@
     <t>2x2</t>
   </si>
   <si>
-    <t>被撞：+10分，如果自身没有撞击别的物品，则自身+2污染</t>
-  </si>
-  <si>
     <t>撞击链条结尾的附加，是缺分数的过渡</t>
   </si>
   <si>
@@ -180,9 +175,6 @@
     <t>废弃物/</t>
   </si>
   <si>
-    <t>被撞：+5分，自身+3污染</t>
-  </si>
-  <si>
     <t>核心快速为自身叠加污染的手段</t>
   </si>
   <si>
@@ -192,9 +184,6 @@
     <t>1x3</t>
   </si>
   <si>
-    <t>被撞：自身所指方向一整行中所有废弃物+1污染</t>
-  </si>
-  <si>
     <t>核心快速群体叠加污染的手段</t>
   </si>
   <si>
@@ -222,149 +211,280 @@
     <t>潮湿纸箱</t>
   </si>
   <si>
+    <t>后期可以为其他物品叠加污染</t>
+  </si>
+  <si>
+    <t>后期作为额外得分终端。</t>
+  </si>
+  <si>
+    <t>生锈齿轮</t>
+  </si>
+  <si>
+    <t>废弃物/机械</t>
+  </si>
+  <si>
+    <t>梦境之种</t>
+  </si>
+  <si>
+    <t>不可抽取</t>
+  </si>
+  <si>
+    <t>4x4</t>
+  </si>
+  <si>
+    <t>5x5</t>
+  </si>
+  <si>
+    <t>根源之梦</t>
+  </si>
+  <si>
+    <t>特殊物品</t>
+  </si>
+  <si>
+    <t>每当你捕梦5次后，撞击！</t>
+  </si>
+  <si>
+    <t>棒球</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂痕镜片</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>破旧闹钟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+3分，如果已经捕梦超过15次，额外+8分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>沿长边方向</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+9分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>易拉罐</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>矿泉水瓶</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果核</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>沿短边方向</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+5分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+5分，复制并触发撞击自己的物品的效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法抽取</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>向右</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>从背包中丢弃时：+3梦值，并且留下一个苹果核</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>每抽取5次：变回苹果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法撞击</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>礼物盒</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>美味烧鸡</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+20分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+5分，自身消失并在所在位置留下一些随机物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+2分，自身+1污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：自身所指方向一整行中废弃物+1污染（不含自身）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+5分，自身+3污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+10分，如果自身没有撞击别的物品，则自身+2污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>被撞：+6分，自身方向上的下一个物品+3污染</t>
-  </si>
-  <si>
-    <t>后期可以为其他物品叠加污染</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>被撞：+25分，净化全场所有污染标记，每净化1层+25分</t>
-  </si>
-  <si>
-    <t>后期作为额外得分终端。</t>
-  </si>
-  <si>
-    <t>生锈齿轮</t>
-  </si>
-  <si>
-    <t>废弃物/机械</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>被撞：+1污染层数，随后将自身污染层数扩散至周围物品</t>
-  </si>
-  <si>
-    <t>梦境之种</t>
-  </si>
-  <si>
-    <t>不可抽取</t>
-  </si>
-  <si>
-    <t>4x4</t>
-  </si>
-  <si>
-    <t>5x5</t>
-  </si>
-  <si>
-    <t>根源之梦</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>小补丁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>直到本局结束，目标物品获得“被撞：+2分”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦值糖</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑墨水</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标废弃物+1污染</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时标签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦境放大镜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>在三个随机物品中选择一个，下次捕梦时必定为此物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3%的梦值</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>皱纸团</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>在目标位置生成一个1x1的废弃物衍生物，具有“被撞：+1分”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹珠</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标物品立刻触发一次“撞击！”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>便宜胶水</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>消毒喷雾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸飞机</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标物品获得废弃物、梦之种或机械标签</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>净化目标废弃物，每净化一层+3分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>大礼包</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标物品本局游戏不能被移动，其获得“被撞：+10分”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>直到本局结束，随机三个物品获得“被撞：+4分”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后，随机获得3个1x1的物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>保险契约</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>特殊物品</t>
-  </si>
-  <si>
-    <t>每当你捕梦5次后，撞击！</t>
-  </si>
-  <si>
-    <t>棒球</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂痕镜片</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>破旧闹钟</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+3分，如果已经捕梦超过15次，额外+8分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>沿长边方向</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+9分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>易拉罐</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>矿泉水瓶</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>苹果</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>苹果核</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>沿短边方向</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分，复制并触发撞击自己的物品的效果</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法抽取</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>向右</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>从背包中丢弃时：+3梦值，并且留下一个苹果核</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>每抽取5次：变回苹果</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法撞击</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>礼物盒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2x2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>美味烧鸡</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+20分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分，自身消失并在所在位置留下一些随机物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>当san值归0但分数不满足要求时：回复5san，然后此物品消失</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有道具</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -919,7 +1039,7 @@
       </c>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -942,10 +1062,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="1"/>
@@ -955,7 +1075,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>23</v>
@@ -973,10 +1093,10 @@
         <v>24</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="1"/>
@@ -986,7 +1106,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>23</v>
@@ -1002,10 +1122,10 @@
         <v>24</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="1"/>
@@ -1015,10 +1135,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D5" s="8">
         <v>-6</v>
@@ -1033,10 +1153,10 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -1047,15 +1167,15 @@
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
     </row>
-    <row r="6" spans="1:20" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="62" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="D6" s="8">
         <v>-10</v>
@@ -1070,10 +1190,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -1089,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>23</v>
@@ -1107,10 +1227,10 @@
         <v>24</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -1126,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="8">
         <v>8</v>
@@ -1142,13 +1262,13 @@
         <v>24</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
@@ -1159,15 +1279,15 @@
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
     </row>
-    <row r="9" spans="1:20" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="8">
         <v>-20</v>
@@ -1176,16 +1296,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -1201,10 +1321,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D10" s="8">
         <v>-25</v>
@@ -1219,10 +1339,10 @@
         <v>10</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -1238,10 +1358,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D11" s="8">
         <v>-25</v>
@@ -1256,10 +1376,10 @@
         <v>24</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -1275,10 +1395,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="8">
         <v>5</v>
@@ -1293,7 +1413,7 @@
         <v>24</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I12" s="8"/>
       <c r="M12" s="8"/>
@@ -1331,10 +1451,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="8">
         <v>-25</v>
@@ -1352,7 +1472,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -1368,10 +1488,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="8">
         <v>-30</v>
@@ -1386,10 +1506,10 @@
         <v>24</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
@@ -1408,7 +1528,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" s="8">
         <v>15</v>
@@ -1423,10 +1543,10 @@
         <v>24</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -1442,7 +1562,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>23</v>
@@ -1454,16 +1574,16 @@
         <v>20</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -2047,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>23</v>
@@ -2056,10 +2176,10 @@
         <v>14</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>24</v>
@@ -2072,16 +2192,16 @@
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>24</v>
@@ -2094,16 +2214,16 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>24</v>
@@ -2116,16 +2236,16 @@
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>24</v>
@@ -2138,16 +2258,16 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>24</v>
@@ -2979,25 +3099,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3005,10 +3125,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -3017,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>9</v>
@@ -3028,10 +3148,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -3040,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3051,10 +3171,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -3063,10 +3183,10 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3074,10 +3194,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -3086,10 +3206,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3097,10 +3217,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -3109,10 +3229,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3120,10 +3240,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -3132,10 +3252,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3143,25 +3263,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3169,10 +3289,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -3181,10 +3301,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3192,10 +3312,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3204,10 +3324,36 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -3408,4 +3554,605 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0EECB-104A-4ADE-A646-4C547272FF2A}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" customWidth="1"/>
+    <col min="8" max="8" width="48.7265625" customWidth="1"/>
+    <col min="9" max="9" width="26.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
+++ b/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E7B5BC-5747-4B36-AE78-D71897533EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4885F93-706F-48DF-8836-D6C87BAAC3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="污染" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="257">
   <si>
     <t>序号</t>
   </si>
@@ -223,18 +223,12 @@
     <t>废弃物/机械</t>
   </si>
   <si>
-    <t>梦境之种</t>
-  </si>
-  <si>
     <t>不可抽取</t>
   </si>
   <si>
     <t>4x4</t>
   </si>
   <si>
-    <t>5x5</t>
-  </si>
-  <si>
     <t>根源之梦</t>
   </si>
   <si>
@@ -486,6 +480,389 @@
   <si>
     <t>稀有道具</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦境之种（1级形态）</t>
+  </si>
+  <si>
+    <t>等级1-9：被撞：+当前等级x1分。升级到10级时尝试变为2x2，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>梦境之种的初始形态，用低占格提供稳定成长起点。</t>
+  </si>
+  <si>
+    <t>发光种子/小嫩芽</t>
+  </si>
+  <si>
+    <t>梦境之种（2级形态）</t>
+  </si>
+  <si>
+    <t>等级10-19：被撞：+当前等级x2分。升级到20级时尝试变为3x3，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>第一次体型成长，开始要求玩家预留空间。</t>
+  </si>
+  <si>
+    <t>双叶幼苗/浅绿色梦光</t>
+  </si>
+  <si>
+    <t>梦境之种（3级形态）</t>
+  </si>
+  <si>
+    <t>等级20-29：被撞：+当前等级x4分。升级到30级时尝试变为4x4，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>中后期核心收益形态，占格压力明显上升。</t>
+  </si>
+  <si>
+    <t>小型梦树/根须扩散</t>
+  </si>
+  <si>
+    <t>梦境之种（4级形态）</t>
+  </si>
+  <si>
+    <t>等级30及以上：被撞：+当前等级x8分。继续升级不会再次变大。</t>
+  </si>
+  <si>
+    <t>梦境流终端，巨大占格换取高额等级收益。</t>
+  </si>
+  <si>
+    <t>大型梦树/树冠发光</t>
+  </si>
+  <si>
+    <t>梦土铲</t>
+  </si>
+  <si>
+    <t>被撞：播种。</t>
+  </si>
+  <si>
+    <t>最基础的播种入口，让撞击链可以制造梦境之种。</t>
+  </si>
+  <si>
+    <t>沾着发光土壤的小铲</t>
+  </si>
+  <si>
+    <t>小喷壶</t>
+  </si>
+  <si>
+    <t>被撞：自身所指方向的第一个梦境之种等级+1；若没有命中梦境之种，+2分。</t>
+  </si>
+  <si>
+    <t>早期低成本升级工具，空场也不完全亏。</t>
+  </si>
+  <si>
+    <t>旧喷壶/蓝色水滴</t>
+  </si>
+  <si>
+    <t>空心果壳</t>
+  </si>
+  <si>
+    <t>从背包中丢弃时：在其原位置播种。若原位置已被占用，则在相邻空格播种。</t>
+  </si>
+  <si>
+    <t>把丢弃路线接入播种，并制造空间决策。</t>
+  </si>
+  <si>
+    <t>裂开的空果壳</t>
+  </si>
+  <si>
+    <t>种子铃铛</t>
+  </si>
+  <si>
+    <t>被撞：相邻所有梦境之种等级+1，每次结算最多影响2个。</t>
+  </si>
+  <si>
+    <t>鼓励把梦境之种围绕触发点摆放。</t>
+  </si>
+  <si>
+    <t>缠着幼芽的小铃铛</t>
+  </si>
+  <si>
+    <t>月露灯</t>
+  </si>
+  <si>
+    <t>每捕梦4次：随机1个梦境之种等级+1；若背包中没有梦境之种，则在随机空格播种。</t>
+  </si>
+  <si>
+    <t>提供稳定的梦种成长节奏，避免完全依赖撞击。</t>
+  </si>
+  <si>
+    <t>盛着月露的提灯</t>
+  </si>
+  <si>
+    <t>育苗托盘</t>
+  </si>
+  <si>
+    <t>每当你播种：+3分。每次捕梦后最多触发2次。</t>
+  </si>
+  <si>
+    <t>让前期多次播种有即时分数，不只服务后期。</t>
+  </si>
+  <si>
+    <t>旧木托盘/小苗格</t>
+  </si>
+  <si>
+    <t>根系导管</t>
+  </si>
+  <si>
+    <t>被撞：自身所指方向一整行中的所有梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>核心横向升级件，要求玩家规划方向和行列。</t>
+  </si>
+  <si>
+    <t>透明管道中流动的绿光</t>
+  </si>
+  <si>
+    <t>温室灯</t>
+  </si>
+  <si>
+    <t>每捕梦5次：等级最高的梦境之种等级+2。若因此变大，+12分。</t>
+  </si>
+  <si>
+    <t>稳定培养一个主种子，是纵向成长核心。</t>
+  </si>
+  <si>
+    <t>旧温室灯/暖色光圈</t>
+  </si>
+  <si>
+    <t>嫁接刀</t>
+  </si>
+  <si>
+    <t>被撞：相邻等级最低的梦境之种等级+2；若目标等级低于10，额外等级+1。</t>
+  </si>
+  <si>
+    <t>帮助新种子追赶等级，支持横向多种子。</t>
+  </si>
+  <si>
+    <t>银色小刀/藤蔓缠柄</t>
+  </si>
+  <si>
+    <t>蔓生罗盘</t>
+  </si>
+  <si>
+    <t>链结束：本次撞击链每命中1个梦境之种，使等级最高的梦境之种等级+1，最多+3。</t>
+  </si>
+  <si>
+    <t>把撞击链长度转化为梦种成长。</t>
+  </si>
+  <si>
+    <t>绿色罗盘/藤蔓指针</t>
+  </si>
+  <si>
+    <t>生态瓶</t>
+  </si>
+  <si>
+    <t>被撞：若背包中只有1个梦境之种，使其等级+3；否则所有梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>在单核巨树和多种子路线之间都能发挥作用。</t>
+  </si>
+  <si>
+    <t>玻璃生态瓶/瓶中小树</t>
+  </si>
+  <si>
+    <t>根网枢纽</t>
+  </si>
+  <si>
+    <t>被撞：每有1个相邻梦境之种，+5分，并使该梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>奖励密集摆放，是梦种与撞击站位的中期核心。</t>
+  </si>
+  <si>
+    <t>铜制根网节点</t>
+  </si>
+  <si>
+    <t>月冠温床</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次有梦境之种达到4x4：+60分。此后每捕梦4次，等级最高的梦境之种等级+2。</t>
+  </si>
+  <si>
+    <t>后期成型补强，奖励完成巨大梦种。</t>
+  </si>
+  <si>
+    <t>月冠形大型温床</t>
+  </si>
+  <si>
+    <t>星根祭坛</t>
+  </si>
+  <si>
+    <t>2x3</t>
+  </si>
+  <si>
+    <t>链结束：若本次撞击链命中过4x4梦境之种，+该梦境之种等级x3分。每个局内关卡限1次。</t>
+  </si>
+  <si>
+    <t>给4x4梦种一个高价值撞击终端。</t>
+  </si>
+  <si>
+    <t>星纹石祭坛/根须光路</t>
+  </si>
+  <si>
+    <t>巨木回声</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次4x4梦境之种被撞后：从该梦境之种发起一次撞击！</t>
+  </si>
+  <si>
+    <t>后期让巨大梦种从纯收益点变成撞击链节点。</t>
+  </si>
+  <si>
+    <t>树心回声纹/发光年轮</t>
+  </si>
+  <si>
+    <t>梦之种</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械/梦之种</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁珠</t>
+  </si>
+  <si>
+    <t>捕梦到另一枚铁珠时：撞击！</t>
+  </si>
+  <si>
+    <t>旧铁珠/轻微锈迹</t>
+  </si>
+  <si>
+    <t>小齿轮</t>
+  </si>
+  <si>
+    <t>被撞：+3分。若本次链已命中2个或以上机械物品，额外+2分。</t>
+  </si>
+  <si>
+    <t>小铜齿轮</t>
+  </si>
+  <si>
+    <t>传动皮带</t>
+  </si>
+  <si>
+    <t>被撞：+4分。若自身成功传导撞击，额外+3分。</t>
+  </si>
+  <si>
+    <t>黑色橡胶皮带</t>
+  </si>
+  <si>
+    <t>顺转弯管</t>
+  </si>
+  <si>
+    <t>机械/传动</t>
+  </si>
+  <si>
+    <t>被撞：顺转传动！每条链限1次。</t>
+  </si>
+  <si>
+    <t>L形铜管/顺时针标记</t>
+  </si>
+  <si>
+    <t>逆转弯管</t>
+  </si>
+  <si>
+    <t>被撞：逆转传动！每条链限1次。</t>
+  </si>
+  <si>
+    <t>L形铁管/逆时针标记</t>
+  </si>
+  <si>
+    <t>制动片</t>
+  </si>
+  <si>
+    <t>被撞：+8分，本条分支停止传导。</t>
+  </si>
+  <si>
+    <t>磨损刹车片</t>
+  </si>
+  <si>
+    <t>齿条</t>
+  </si>
+  <si>
+    <t>被撞：+本次链机械命中数分，最多+10分。若自身成功传导撞击，额外+4分。</t>
+  </si>
+  <si>
+    <t>长条齿轨</t>
+  </si>
+  <si>
+    <t>差速器</t>
+  </si>
+  <si>
+    <t>链结束：+本次链机械命中数x2分；若本次链转向次数大于等于2，额外+10分。</t>
+  </si>
+  <si>
+    <t>齿轮差速器</t>
+  </si>
+  <si>
+    <t>双轴转轮</t>
+  </si>
+  <si>
+    <t>被撞：若本次链机械命中数大于等于3，双向传动！每条链限1次。</t>
+  </si>
+  <si>
+    <t>双层转轮</t>
+  </si>
+  <si>
+    <t>蓄能飞轮</t>
+  </si>
+  <si>
+    <t>每当本次链累计命中3个机械物品：+12分。每条链最多触发2次。</t>
+  </si>
+  <si>
+    <t>发光飞轮</t>
+  </si>
+  <si>
+    <t>曲轴</t>
+  </si>
+  <si>
+    <t>被撞：逆转传动！若该传动命中机械物品，+10分。每条链限1次。</t>
+  </si>
+  <si>
+    <t>弯折曲轴</t>
+  </si>
+  <si>
+    <t>计数轮</t>
+  </si>
+  <si>
+    <t>链结束：若本次链命中大于等于6个物品，+18分；若大于等于9个，改为+32分。</t>
+  </si>
+  <si>
+    <t>数字计数轮</t>
+  </si>
+  <si>
+    <t>中央引擎</t>
+  </si>
+  <si>
+    <t>机械/核心</t>
+  </si>
+  <si>
+    <t>链结束：若本次链机械命中数大于等于10，+60分；若本次链转向次数大于等于3，额外+30分。</t>
+  </si>
+  <si>
+    <t>小型梦境引擎</t>
+  </si>
+  <si>
+    <t>终端计算机</t>
+  </si>
+  <si>
+    <t>链结束：+本次链机械命中数x3分，最多+45分；若本次链包含双向传动，额外+15分。</t>
+  </si>
+  <si>
+    <t>旧终端屏幕/齿轮接口</t>
+  </si>
+  <si>
+    <t>星环轴承</t>
+  </si>
+  <si>
+    <t>机械/传动/核心</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次被撞：全向传动！这些分支不能再次触发星环轴承。</t>
+  </si>
+  <si>
+    <t>星环形轴承</t>
   </si>
 </sst>
 </file>
@@ -677,8 +1054,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,7 +1439,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>25</v>
@@ -1190,7 +1567,7 @@
         <v>24</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>38</v>
@@ -1302,7 +1679,7 @@
         <v>15</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>48</v>
@@ -1339,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>51</v>
@@ -1506,7 +1883,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>60</v>
@@ -1543,7 +1920,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>61</v>
@@ -1580,7 +1957,7 @@
         <v>24</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>60</v>
@@ -2081,36 +2458,474 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="76.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>232</v>
+      </c>
+      <c r="I9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>247</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>248</v>
+      </c>
+      <c r="I14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>247</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>251</v>
+      </c>
+      <c r="I15" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2124,930 +2939,656 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="8" max="8" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" t="s">
+        <v>164</v>
+      </c>
+      <c r="J10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I11" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>208</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="B15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8" t="s">
+      <c r="H15" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>191</v>
+      </c>
+      <c r="I17" t="s">
+        <v>192</v>
+      </c>
+      <c r="J17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18">
         <v>14</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="H18" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" t="s">
+        <v>196</v>
+      </c>
+      <c r="J18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20">
+        <v>26</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-    </row>
-    <row r="49" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-    </row>
-    <row r="50" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-    </row>
-    <row r="52" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-    </row>
-    <row r="53" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-    </row>
-    <row r="54" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-    </row>
-    <row r="56" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-    </row>
-    <row r="57" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-    </row>
-    <row r="58" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-    </row>
-    <row r="59" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-    </row>
-    <row r="60" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-    </row>
-    <row r="61" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-    </row>
-    <row r="62" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-    </row>
-    <row r="63" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-    </row>
-    <row r="64" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-    </row>
-    <row r="65" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-    </row>
-    <row r="66" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-    </row>
-    <row r="67" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-    </row>
-    <row r="68" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-    </row>
-    <row r="69" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-    </row>
-    <row r="70" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
+      <c r="H20" t="s">
+        <v>204</v>
+      </c>
+      <c r="I20" t="s">
+        <v>205</v>
+      </c>
+      <c r="J20" t="s">
+        <v>206</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3099,25 +3640,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3125,10 +3666,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -3137,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>9</v>
@@ -3148,10 +3689,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -3160,10 +3701,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3171,10 +3712,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -3183,10 +3724,10 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3194,10 +3735,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -3206,10 +3747,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3217,10 +3758,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -3229,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3240,10 +3781,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -3252,10 +3793,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3263,25 +3804,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3289,10 +3830,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -3301,10 +3842,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3312,10 +3853,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3324,10 +3865,10 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3335,10 +3876,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12">
         <v>20</v>
@@ -3347,13 +3888,13 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -3604,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -3616,13 +4157,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
         <v>106</v>
       </c>
-      <c r="G2" t="s">
-        <v>108</v>
-      </c>
       <c r="H2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3630,10 +4171,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -3642,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" t="s">
         <v>106</v>
       </c>
-      <c r="G3" t="s">
-        <v>108</v>
-      </c>
       <c r="H3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3656,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -3668,13 +4209,13 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" t="s">
         <v>106</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>108</v>
-      </c>
-      <c r="H4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3682,7 +4223,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -3694,13 +4235,13 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
         <v>106</v>
       </c>
-      <c r="G5" t="s">
-        <v>108</v>
-      </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3708,7 +4249,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -3720,13 +4261,13 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
         <v>106</v>
       </c>
-      <c r="G6" t="s">
-        <v>108</v>
-      </c>
       <c r="H6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3734,7 +4275,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -3746,13 +4287,13 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" t="s">
         <v>106</v>
       </c>
-      <c r="G7" t="s">
-        <v>108</v>
-      </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3760,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -3772,13 +4313,13 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" t="s">
         <v>106</v>
       </c>
-      <c r="G8" t="s">
-        <v>108</v>
-      </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3786,7 +4327,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -3798,13 +4339,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" t="s">
         <v>106</v>
       </c>
-      <c r="G9" t="s">
-        <v>108</v>
-      </c>
       <c r="H9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3812,7 +4353,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -3824,13 +4365,13 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
         <v>106</v>
       </c>
-      <c r="G10" t="s">
-        <v>108</v>
-      </c>
       <c r="H10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3838,10 +4379,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11">
         <v>18</v>
@@ -3850,13 +4391,13 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" t="s">
         <v>106</v>
       </c>
-      <c r="G11" t="s">
-        <v>108</v>
-      </c>
       <c r="H11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3867,10 +4408,10 @@
         <v>23</v>
       </c>
       <c r="F12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" t="s">
         <v>106</v>
-      </c>
-      <c r="G12" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -3881,10 +4422,10 @@
         <v>23</v>
       </c>
       <c r="F13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" t="s">
         <v>106</v>
-      </c>
-      <c r="G13" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -3895,10 +4436,10 @@
         <v>23</v>
       </c>
       <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" t="s">
         <v>106</v>
-      </c>
-      <c r="G14" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -3909,10 +4450,10 @@
         <v>23</v>
       </c>
       <c r="F15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" t="s">
         <v>106</v>
-      </c>
-      <c r="G15" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -3923,10 +4464,10 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" t="s">
         <v>106</v>
-      </c>
-      <c r="G16" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -3937,10 +4478,10 @@
         <v>23</v>
       </c>
       <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
         <v>106</v>
-      </c>
-      <c r="G17" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -3951,10 +4492,10 @@
         <v>23</v>
       </c>
       <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -3965,10 +4506,10 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
         <v>106</v>
-      </c>
-      <c r="G19" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3979,10 +4520,10 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" t="s">
         <v>106</v>
-      </c>
-      <c r="G20" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3990,7 +4531,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -4002,13 +4543,13 @@
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -4019,10 +4560,10 @@
         <v>23</v>
       </c>
       <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s">
         <v>106</v>
-      </c>
-      <c r="G22" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -4033,10 +4574,10 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" t="s">
         <v>106</v>
-      </c>
-      <c r="G23" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -4047,10 +4588,10 @@
         <v>23</v>
       </c>
       <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
         <v>106</v>
-      </c>
-      <c r="G24" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -4061,10 +4602,10 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" t="s">
         <v>106</v>
-      </c>
-      <c r="G25" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -4075,10 +4616,10 @@
         <v>23</v>
       </c>
       <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
         <v>106</v>
-      </c>
-      <c r="G26" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -4089,10 +4630,10 @@
         <v>23</v>
       </c>
       <c r="F27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" t="s">
         <v>106</v>
-      </c>
-      <c r="G27" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -4103,10 +4644,10 @@
         <v>23</v>
       </c>
       <c r="F28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" t="s">
         <v>106</v>
-      </c>
-      <c r="G28" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -4117,10 +4658,10 @@
         <v>23</v>
       </c>
       <c r="F29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s">
         <v>106</v>
-      </c>
-      <c r="G29" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -4131,10 +4672,10 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
         <v>106</v>
-      </c>
-      <c r="G30" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -4145,10 +4686,10 @@
         <v>23</v>
       </c>
       <c r="F31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" t="s">
         <v>106</v>
-      </c>
-      <c r="G31" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
+++ b/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
@@ -29,207 +29,623 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="232">
   <si>
     <t>序号</t>
   </si>
   <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>格子</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>梦值消耗</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>方向</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>设计目的</t>
+  </si>
+  <si>
+    <t>视觉效果</t>
+  </si>
+  <si>
+    <t>纸团</t>
+  </si>
+  <si>
+    <t>1x1</t>
+  </si>
+  <si>
+    <t>废弃物</t>
+  </si>
+  <si>
+    <t>向右</t>
+  </si>
+  <si>
+    <t>被撞：+2分，自身+1污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>最基本的本体叠加污染手段</t>
+  </si>
+  <si>
+    <t>joker（一张废弃扑克牌）</t>
+  </si>
+  <si>
+    <t>被撞：+3分</t>
+  </si>
+  <si>
+    <t>废弃物中的白板，需要配合别人叠加污染层数来发挥作用。</t>
+  </si>
+  <si>
+    <t>便利贴</t>
+  </si>
+  <si>
+    <t>每当有3层污染叠加：+10分</t>
+  </si>
+  <si>
+    <t>前期在层数不足时，提供分数增益。本身不是废弃物，自己不便于叠污染。</t>
+  </si>
+  <si>
+    <t>漏水钢笔</t>
+  </si>
+  <si>
+    <t>1x2</t>
+  </si>
+  <si>
+    <t>沿长边方向</t>
+  </si>
+  <si>
+    <t>被撞：+3分，自身所指方向的下一个物品如果是废弃物，其+1污染</t>
+  </si>
+  <si>
+    <t>最基本的为另一个废弃物叠加污染的手段</t>
+  </si>
+  <si>
+    <t>伤心泰迪熊</t>
+  </si>
+  <si>
+    <t>2x2</t>
+  </si>
+  <si>
+    <t>被撞：+10分，如果自身没有撞击别的物品，则自身+2污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>撞击结算条结尾的附加，是缺分数的过渡</t>
+  </si>
+  <si>
+    <t>小药瓶</t>
+  </si>
+  <si>
+    <t>被撞：污染层数最高的物品污染+1</t>
+  </si>
+  <si>
+    <t>最基本的定向叠加污染的手段</t>
+  </si>
+  <si>
+    <t>垃圾袋</t>
+  </si>
+  <si>
+    <t>被撞：净化与自身相邻所有物品的污染层数，每净化1层回复1点梦值</t>
+  </si>
+  <si>
+    <t>污染流非常少的回复梦值的手段，可以作为分数够后回梦值补发育的物品</t>
+  </si>
+  <si>
+    <t>一卷垃圾袋</t>
+  </si>
+  <si>
+    <t>过期药物</t>
+  </si>
+  <si>
+    <t>废弃物/</t>
+  </si>
+  <si>
+    <t>沿短边方向</t>
+  </si>
+  <si>
+    <t>被撞：+5分，自身+3污染，增加污染效果不会重复触发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心快速为自身叠加污染的手段</t>
+  </si>
+  <si>
+    <t>针管</t>
+  </si>
+  <si>
+    <t>1x3</t>
+  </si>
+  <si>
+    <t>被撞：自身所指方向一整行中废弃物+1污染（不含自身）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心快速群体叠加污染的手段</t>
+  </si>
+  <si>
+    <t>剩饭盒</t>
+  </si>
+  <si>
+    <t>3x3</t>
+  </si>
+  <si>
+    <t>被撞：相邻所有废弃物+1污染</t>
+  </si>
+  <si>
+    <t>隔离箱</t>
+  </si>
+  <si>
+    <t>机械</t>
+  </si>
+  <si>
+    <t>污染层数导致的梦值扣除效应-1</t>
+  </si>
+  <si>
+    <t>旧足球</t>
+  </si>
+  <si>
+    <t>捕梦到废弃物时：撞击！</t>
+  </si>
+  <si>
+    <t>废弃物系列的额外撞击源</t>
+  </si>
+  <si>
+    <t>潮湿纸箱</t>
+  </si>
+  <si>
+    <t>被撞：+6分，自身方向上的下一个物品+3污染</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>后期可以为其他物品叠加污染</t>
+  </si>
+  <si>
+    <t>垃圾回收器</t>
+  </si>
+  <si>
+    <t>被撞：+25分，净化全场所有污染标记，每净化1层+25分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>后期作为额外得分终端。</t>
+  </si>
+  <si>
+    <t>生锈齿轮</t>
+  </si>
+  <si>
+    <t>废弃物/机械</t>
+  </si>
+  <si>
+    <t>被撞：+1污染层数，随后将自身污染层数扩散至周围物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>物品名称</t>
   </si>
   <si>
     <t>占据格子数</t>
   </si>
   <si>
-    <t>价值</t>
-  </si>
-  <si>
     <t>类别</t>
   </si>
   <si>
-    <t>基础消耗san</t>
-  </si>
-  <si>
-    <t>方向</t>
-  </si>
-  <si>
-    <t>效果</t>
-  </si>
-  <si>
-    <t>视觉效果</t>
-  </si>
-  <si>
-    <t>捕梦到另一枚棒球时：撞击！</t>
-  </si>
-  <si>
-    <t>沿长边方向</t>
-  </si>
-  <si>
-    <t>废弃物</t>
-  </si>
-  <si>
-    <t>捕梦到废弃物时：撞击！</t>
-  </si>
-  <si>
-    <t>机械</t>
+    <t>基础梦值消耗</t>
+  </si>
+  <si>
+    <t>铁珠</t>
+  </si>
+  <si>
+    <t>捕梦到另一枚铁珠时：撞击！</t>
+  </si>
+  <si>
+    <t>旧铁珠/轻微锈迹</t>
+  </si>
+  <si>
+    <t>小齿轮</t>
+  </si>
+  <si>
+    <t>被撞：+3分。若本次撞击结算已命中2个或以上机械物品，额外+2分。</t>
+  </si>
+  <si>
+    <t>小铜齿轮</t>
+  </si>
+  <si>
+    <t>传动皮带</t>
+  </si>
+  <si>
+    <t>被撞：+4分。若自身让本次撞击结算继续命中下一个物品，额外+3分。</t>
+  </si>
+  <si>
+    <t>黑色橡胶皮带</t>
+  </si>
+  <si>
+    <t>左传动弯管</t>
+  </si>
+  <si>
+    <t>机械/传动</t>
+  </si>
+  <si>
+    <t>被撞：向左传动！每次撞击结算限1次。</t>
+  </si>
+  <si>
+    <t>L形铜管/左侧箭头标记</t>
+  </si>
+  <si>
+    <t>右传动弯管</t>
+  </si>
+  <si>
+    <t>被撞：向右传动！每次撞击结算限1次。</t>
+  </si>
+  <si>
+    <t>L形铁管/右侧箭头标记</t>
+  </si>
+  <si>
+    <t>制动片</t>
+  </si>
+  <si>
+    <t>被撞：+8分，本分支停止传导。</t>
+  </si>
+  <si>
+    <t>磨损刹车片</t>
+  </si>
+  <si>
+    <t>齿条</t>
+  </si>
+  <si>
+    <t>被撞：+本次命中机械物品数分，最多+10分。若自身让本次撞击结算继续命中下一个物品，额外+4分。</t>
+  </si>
+  <si>
+    <t>长条齿轨</t>
+  </si>
+  <si>
+    <t>差速器</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：+本次命中机械物品数x2分；若本次转向传动次数大于等于2，额外+10分。</t>
+  </si>
+  <si>
+    <t>齿轮差速器</t>
+  </si>
+  <si>
+    <t>双轴转轮</t>
+  </si>
+  <si>
+    <t>被撞：若本次命中机械物品数大于等于3，双向传动！每次撞击结算限1次。</t>
+  </si>
+  <si>
+    <t>双层转轮</t>
+  </si>
+  <si>
+    <t>蓄能飞轮</t>
+  </si>
+  <si>
+    <t>每当本次撞击结算累计命中3个机械物品：+12分。每次撞击结算最多触发2次。</t>
+  </si>
+  <si>
+    <t>发光飞轮</t>
+  </si>
+  <si>
+    <t>曲轴</t>
+  </si>
+  <si>
+    <t>被撞：向右传动！若该传动命中机械物品，+10分。每次撞击结算限1次。</t>
+  </si>
+  <si>
+    <t>弯折曲轴</t>
+  </si>
+  <si>
+    <t>计数轮</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：若本次命中物品数大于等于6，+18分；若大于等于9，改为+32分。</t>
+  </si>
+  <si>
+    <t>数字计数轮</t>
+  </si>
+  <si>
+    <t>中央引擎</t>
+  </si>
+  <si>
+    <t>机械/核心</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：若本次命中机械物品数大于等于10，+60分；若本次转向传动次数大于等于3，额外+30分。</t>
+  </si>
+  <si>
+    <t>小型梦境引擎</t>
+  </si>
+  <si>
+    <t>终端计算机</t>
+  </si>
+  <si>
+    <t>2x3</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：+本次命中机械物品数x3分，最多+45分；若本次撞击结算包含双向传动，额外+15分。</t>
+  </si>
+  <si>
+    <t>旧终端屏幕/齿轮接口</t>
+  </si>
+  <si>
+    <t>星环轴承</t>
+  </si>
+  <si>
+    <t>机械/传动/核心</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次被撞：全向传动！这些分支不能再次触发星环轴承。</t>
+  </si>
+  <si>
+    <t>星环形轴承</t>
+  </si>
+  <si>
+    <t>梦境之种（1级形态）</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
-    <t>沿短边方向</t>
-  </si>
-  <si>
-    <t>垃圾回收器</t>
-  </si>
-  <si>
-    <t>纸团</t>
-  </si>
-  <si>
-    <t>物品</t>
-  </si>
-  <si>
-    <t>格子</t>
-  </si>
-  <si>
-    <t>San</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>设计目的</t>
+    <t>不可抽取</t>
+  </si>
+  <si>
+    <t>梦之种</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级1-9：被撞：+当前等级x1分。升级到10级时尝试变为2x2，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>梦境之种的初始形态，用低占格提供稳定成长起点。</t>
+  </si>
+  <si>
+    <t>发光种子/小嫩芽</t>
+  </si>
+  <si>
+    <t>梦境之种（2级形态）</t>
+  </si>
+  <si>
+    <t>等级10-19：被撞：+当前等级x2分。升级到20级时尝试变为3x3，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>第一次体型成长，开始要求玩家预留空间。</t>
+  </si>
+  <si>
+    <t>双叶幼苗/浅绿色梦光</t>
+  </si>
+  <si>
+    <t>梦境之种（3级形态）</t>
+  </si>
+  <si>
+    <t>等级20-29：被撞：+当前等级x4分。升级到30级时尝试变为4x4，若空间不足则掉出背包。</t>
+  </si>
+  <si>
+    <t>中后期核心收益形态，占格压力明显上升。</t>
+  </si>
+  <si>
+    <t>小型梦树/根须扩散</t>
+  </si>
+  <si>
+    <t>梦境之种（4级形态）</t>
+  </si>
+  <si>
+    <t>4x4</t>
+  </si>
+  <si>
+    <t>等级30及以上：被撞：+当前等级x8分。继续升级不会再次变大。</t>
+  </si>
+  <si>
+    <t>梦境流终端，巨大占格换取高额等级收益。</t>
+  </si>
+  <si>
+    <t>大型梦树/树冠发光</t>
+  </si>
+  <si>
+    <t>梦土铲</t>
+  </si>
+  <si>
+    <t>被撞：播种。</t>
+  </si>
+  <si>
+    <t>最基础的播种入口，让撞击结算可以制造梦境之种。</t>
+  </si>
+  <si>
+    <t>沾着发光土壤的小铲</t>
+  </si>
+  <si>
+    <t>小喷壶</t>
+  </si>
+  <si>
+    <t>被撞：自身所指方向的第一个梦境之种等级+1；若没有命中梦境之种，+2分。</t>
+  </si>
+  <si>
+    <t>早期低成本升级工具，空场也不完全亏。</t>
+  </si>
+  <si>
+    <t>旧喷壶/蓝色水滴</t>
+  </si>
+  <si>
+    <t>空心果壳</t>
+  </si>
+  <si>
+    <t>无法撞击</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>从背包中丢弃时：在其原位置播种。若原位置已被占用，则在相邻空格播种。</t>
+  </si>
+  <si>
+    <t>把丢弃路线接入播种，并制造空间决策。</t>
+  </si>
+  <si>
+    <t>裂开的空果壳</t>
+  </si>
+  <si>
+    <t>种子铃铛</t>
+  </si>
+  <si>
+    <t>被撞：相邻所有梦境之种等级+1，每次结算最多影响2个。</t>
+  </si>
+  <si>
+    <t>鼓励把梦境之种围绕触发点摆放。</t>
+  </si>
+  <si>
+    <t>缠着幼芽的小铃铛</t>
+  </si>
+  <si>
+    <t>月露灯</t>
+  </si>
+  <si>
+    <t>每捕梦4次：随机1个梦境之种等级+1；若背包中没有梦境之种，则在随机空格播种。</t>
+  </si>
+  <si>
+    <t>提供稳定的梦种成长节奏，避免完全依赖撞击。</t>
+  </si>
+  <si>
+    <t>盛着月露的提灯</t>
+  </si>
+  <si>
+    <t>育苗托盘</t>
+  </si>
+  <si>
+    <t>每当你播种：+3分。每次捕梦后最多触发2次。</t>
+  </si>
+  <si>
+    <t>让前期多次播种有即时分数，不只服务后期。</t>
+  </si>
+  <si>
+    <t>旧木托盘/小苗格</t>
+  </si>
+  <si>
+    <t>根系导管</t>
+  </si>
+  <si>
+    <t>机械/梦之种</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：自身所指方向一整行中的所有梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>核心横向升级件，要求玩家规划方向和行列。</t>
+  </si>
+  <si>
+    <t>透明管道中流动的绿光</t>
+  </si>
+  <si>
+    <t>温室灯</t>
+  </si>
+  <si>
+    <t>每捕梦5次：等级最高的梦境之种等级+2。若因此变大，+12分。</t>
+  </si>
+  <si>
+    <t>稳定培养一个主种子，是纵向成长核心。</t>
+  </si>
+  <si>
+    <t>旧温室灯/暖色光圈</t>
+  </si>
+  <si>
+    <t>嫁接刀</t>
+  </si>
+  <si>
+    <t>被撞：相邻等级最低的梦境之种等级+2；若目标等级低于10，额外等级+1。</t>
+  </si>
+  <si>
+    <t>帮助新种子追赶等级，支持横向多种子。</t>
+  </si>
+  <si>
+    <t>银色小刀/藤蔓缠柄</t>
+  </si>
+  <si>
+    <t>蔓生罗盘</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：本次命中的梦境之种每有1个，使等级最高的梦境之种等级+1，最多+3。</t>
+  </si>
+  <si>
+    <t>把撞击命中数转化为梦种成长。</t>
+  </si>
+  <si>
+    <t>绿色罗盘/藤蔓指针</t>
+  </si>
+  <si>
+    <t>生态瓶</t>
+  </si>
+  <si>
+    <t>被撞：若背包中只有1个梦境之种，使其等级+3；否则所有梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>在单核巨树和多种子路线之间都能发挥作用。</t>
+  </si>
+  <si>
+    <t>玻璃生态瓶/瓶中小树</t>
+  </si>
+  <si>
+    <t>根网枢纽</t>
+  </si>
+  <si>
+    <t>被撞：每有1个相邻梦境之种，+5分，并使该梦境之种等级+1。</t>
+  </si>
+  <si>
+    <t>奖励密集摆放，是梦种与撞击站位的中期核心。</t>
+  </si>
+  <si>
+    <t>铜制根网节点</t>
+  </si>
+  <si>
+    <t>月冠温床</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次有梦境之种达到4x4：+60分。此后每捕梦4次，等级最高的梦境之种等级+2。</t>
+  </si>
+  <si>
+    <t>后期成型补强，奖励完成巨大梦种。</t>
+  </si>
+  <si>
+    <t>月冠形大型温床</t>
+  </si>
+  <si>
+    <t>星根祭坛</t>
+  </si>
+  <si>
+    <t>本次撞击结算全部停止后：若本次命中过4x4梦境之种，+该梦境之种等级x3分。每个局内关卡限1次。</t>
+  </si>
+  <si>
+    <t>给4x4梦种一个高价值撞击终端。</t>
+  </si>
+  <si>
+    <t>星纹石祭坛/根须光路</t>
+  </si>
+  <si>
+    <t>巨木回声</t>
+  </si>
+  <si>
+    <t>每个局内关卡第一次4x4梦境之种被撞后：从该梦境之种发起一次撞击！</t>
+  </si>
+  <si>
+    <t>后期让巨大梦种从纯收益点变成撞击结算中的节点。</t>
+  </si>
+  <si>
+    <t>树心回声纹/发光年轮</t>
+  </si>
+  <si>
+    <t>根源之梦</t>
   </si>
   <si>
     <t>1x1</t>
-  </si>
-  <si>
-    <t>向右</t>
-  </si>
-  <si>
-    <t>最基本的本体叠加污染手段</t>
-  </si>
-  <si>
-    <t>joker（一张废弃扑克牌）</t>
-  </si>
-  <si>
-    <t>被撞：+3分</t>
-  </si>
-  <si>
-    <t>废弃物中的白板，需要配合别人叠加污染层数来发挥作用。</t>
-  </si>
-  <si>
-    <t>便利贴</t>
-  </si>
-  <si>
-    <t>每当有3层污染叠加：+10分</t>
-  </si>
-  <si>
-    <t>前期在层数不足时，提供分数增益。本身不是废弃物，自己不便于叠污染。</t>
-  </si>
-  <si>
-    <t>漏水钢笔</t>
-  </si>
-  <si>
-    <t>1x2</t>
-  </si>
-  <si>
-    <t>被撞：+3分，自身所指方向的下一个物品如果是废弃物，其+1污染</t>
-  </si>
-  <si>
-    <t>最基本的为另一个废弃物叠加污染的手段</t>
-  </si>
-  <si>
-    <t>伤心泰迪熊</t>
-  </si>
-  <si>
-    <t>2x2</t>
-  </si>
-  <si>
-    <t>撞击链条结尾的附加，是缺分数的过渡</t>
-  </si>
-  <si>
-    <t>小药瓶</t>
-  </si>
-  <si>
-    <t>被撞：污染层数最高的物品污染+1</t>
-  </si>
-  <si>
-    <t>最基本的定向叠加污染的手段</t>
-  </si>
-  <si>
-    <t>垃圾袋</t>
-  </si>
-  <si>
-    <t>被撞：净化与自身相邻所有物品的污染层数，每净化1层回复1点梦值</t>
-  </si>
-  <si>
-    <t>污染流非常少的回复梦值的手段，可以作为分数够后回san补发育的物品</t>
-  </si>
-  <si>
-    <t>一卷垃圾袋</t>
-  </si>
-  <si>
-    <t>过期药物</t>
-  </si>
-  <si>
-    <t>废弃物/</t>
-  </si>
-  <si>
-    <t>核心快速为自身叠加污染的手段</t>
-  </si>
-  <si>
-    <t>针管</t>
-  </si>
-  <si>
-    <t>1x3</t>
-  </si>
-  <si>
-    <t>核心快速群体叠加污染的手段</t>
-  </si>
-  <si>
-    <t>剩饭盒</t>
-  </si>
-  <si>
-    <t>3x3</t>
-  </si>
-  <si>
-    <t>被撞：相邻所有废弃物+1污染</t>
-  </si>
-  <si>
-    <t>隔离箱</t>
-  </si>
-  <si>
-    <t>污染层数导致的梦值扣除效应-1</t>
-  </si>
-  <si>
-    <t>旧足球</t>
-  </si>
-  <si>
-    <t>废弃物系列的额外撞击源</t>
-  </si>
-  <si>
-    <t>潮湿纸箱</t>
-  </si>
-  <si>
-    <t>后期可以为其他物品叠加污染</t>
-  </si>
-  <si>
-    <t>后期作为额外得分终端。</t>
-  </si>
-  <si>
-    <t>生锈齿轮</t>
-  </si>
-  <si>
-    <t>废弃物/机械</t>
-  </si>
-  <si>
-    <t>不可抽取</t>
-  </si>
-  <si>
-    <t>4x4</t>
-  </si>
-  <si>
-    <t>根源之梦</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>特殊物品</t>
@@ -242,22 +658,25 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>向右</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>捕梦到另一枚棒球时：撞击！</t>
+  </si>
+  <si>
+    <t>破旧闹钟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+3分，如果已经捕梦超过15次，额外+8分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>裂痕镜片</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>破旧闹钟</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+3分，如果已经捕梦超过15次，额外+8分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>1x2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -266,47 +685,47 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>被撞：+5分，复制并触发撞击自己的物品的效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>易拉罐</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>被撞：+9分</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>易拉罐</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>矿泉水瓶</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>沿短边方向</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>被撞：+5分</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>苹果</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>从背包中丢弃时：+3梦值，并且留下一个苹果核</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>苹果核</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>沿短边方向</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分，复制并触发撞击自己的物品的效果</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>无法抽取</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>向右</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>从背包中丢弃时：+3梦值，并且留下一个苹果核</t>
+    <t>衍生物品</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -314,14 +733,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>无法撞击</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>礼物盒</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -330,6 +741,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>被撞：+5分，自身消失并在所在位置留下一些随机物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>美味烧鸡</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -338,134 +753,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>被撞：+5分，自身消失并在所在位置留下一些随机物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+2分，自身+1污染，增加污染效果不会重复触发</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：自身所指方向一整行中废弃物+1污染（不含自身）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+5分，自身+3污染，增加污染效果不会重复触发</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+10分，如果自身没有撞击别的物品，则自身+2污染，增加污染效果不会重复触发</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+6分，自身方向上的下一个物品+3污染</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+25分，净化全场所有污染标记，每净化1层+25分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>被撞：+1污染层数，随后将自身污染层数扩散至周围物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>小补丁</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>直到本局结束，目标物品获得“被撞：+2分”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>梦值糖</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑墨水</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标废弃物+1污染</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>临时标签</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>梦境放大镜</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>在三个随机物品中选择一个，下次捕梦时必定为此物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得3%的梦值</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>皱纸团</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>在目标位置生成一个1x1的废弃物衍生物，具有“被撞：+1分”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>弹珠</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标物品立刻触发一次“撞击！”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>便宜胶水</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>消毒喷雾</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>纸飞机</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标物品获得废弃物、梦之种或机械标签</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>净化目标废弃物，每净化一层+3分</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>大礼包</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标物品本局游戏不能被移动，其获得“被撞：+10分”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>直到本局结束，随机三个物品获得“被撞：+4分”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用后，随机获得3个1x1的物品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>保险契约</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -474,395 +761,8 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当san值归0但分数不满足要求时：回复5san，然后此物品消失</t>
+    <t>当梦值归0但分数不满足要求时：回复5梦值，然后此物品消失</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>稀有道具</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>梦境之种（1级形态）</t>
-  </si>
-  <si>
-    <t>等级1-9：被撞：+当前等级x1分。升级到10级时尝试变为2x2，若空间不足则掉出背包。</t>
-  </si>
-  <si>
-    <t>梦境之种的初始形态，用低占格提供稳定成长起点。</t>
-  </si>
-  <si>
-    <t>发光种子/小嫩芽</t>
-  </si>
-  <si>
-    <t>梦境之种（2级形态）</t>
-  </si>
-  <si>
-    <t>等级10-19：被撞：+当前等级x2分。升级到20级时尝试变为3x3，若空间不足则掉出背包。</t>
-  </si>
-  <si>
-    <t>第一次体型成长，开始要求玩家预留空间。</t>
-  </si>
-  <si>
-    <t>双叶幼苗/浅绿色梦光</t>
-  </si>
-  <si>
-    <t>梦境之种（3级形态）</t>
-  </si>
-  <si>
-    <t>等级20-29：被撞：+当前等级x4分。升级到30级时尝试变为4x4，若空间不足则掉出背包。</t>
-  </si>
-  <si>
-    <t>中后期核心收益形态，占格压力明显上升。</t>
-  </si>
-  <si>
-    <t>小型梦树/根须扩散</t>
-  </si>
-  <si>
-    <t>梦境之种（4级形态）</t>
-  </si>
-  <si>
-    <t>等级30及以上：被撞：+当前等级x8分。继续升级不会再次变大。</t>
-  </si>
-  <si>
-    <t>梦境流终端，巨大占格换取高额等级收益。</t>
-  </si>
-  <si>
-    <t>大型梦树/树冠发光</t>
-  </si>
-  <si>
-    <t>梦土铲</t>
-  </si>
-  <si>
-    <t>被撞：播种。</t>
-  </si>
-  <si>
-    <t>最基础的播种入口，让撞击链可以制造梦境之种。</t>
-  </si>
-  <si>
-    <t>沾着发光土壤的小铲</t>
-  </si>
-  <si>
-    <t>小喷壶</t>
-  </si>
-  <si>
-    <t>被撞：自身所指方向的第一个梦境之种等级+1；若没有命中梦境之种，+2分。</t>
-  </si>
-  <si>
-    <t>早期低成本升级工具，空场也不完全亏。</t>
-  </si>
-  <si>
-    <t>旧喷壶/蓝色水滴</t>
-  </si>
-  <si>
-    <t>空心果壳</t>
-  </si>
-  <si>
-    <t>从背包中丢弃时：在其原位置播种。若原位置已被占用，则在相邻空格播种。</t>
-  </si>
-  <si>
-    <t>把丢弃路线接入播种，并制造空间决策。</t>
-  </si>
-  <si>
-    <t>裂开的空果壳</t>
-  </si>
-  <si>
-    <t>种子铃铛</t>
-  </si>
-  <si>
-    <t>被撞：相邻所有梦境之种等级+1，每次结算最多影响2个。</t>
-  </si>
-  <si>
-    <t>鼓励把梦境之种围绕触发点摆放。</t>
-  </si>
-  <si>
-    <t>缠着幼芽的小铃铛</t>
-  </si>
-  <si>
-    <t>月露灯</t>
-  </si>
-  <si>
-    <t>每捕梦4次：随机1个梦境之种等级+1；若背包中没有梦境之种，则在随机空格播种。</t>
-  </si>
-  <si>
-    <t>提供稳定的梦种成长节奏，避免完全依赖撞击。</t>
-  </si>
-  <si>
-    <t>盛着月露的提灯</t>
-  </si>
-  <si>
-    <t>育苗托盘</t>
-  </si>
-  <si>
-    <t>每当你播种：+3分。每次捕梦后最多触发2次。</t>
-  </si>
-  <si>
-    <t>让前期多次播种有即时分数，不只服务后期。</t>
-  </si>
-  <si>
-    <t>旧木托盘/小苗格</t>
-  </si>
-  <si>
-    <t>根系导管</t>
-  </si>
-  <si>
-    <t>被撞：自身所指方向一整行中的所有梦境之种等级+1。</t>
-  </si>
-  <si>
-    <t>核心横向升级件，要求玩家规划方向和行列。</t>
-  </si>
-  <si>
-    <t>透明管道中流动的绿光</t>
-  </si>
-  <si>
-    <t>温室灯</t>
-  </si>
-  <si>
-    <t>每捕梦5次：等级最高的梦境之种等级+2。若因此变大，+12分。</t>
-  </si>
-  <si>
-    <t>稳定培养一个主种子，是纵向成长核心。</t>
-  </si>
-  <si>
-    <t>旧温室灯/暖色光圈</t>
-  </si>
-  <si>
-    <t>嫁接刀</t>
-  </si>
-  <si>
-    <t>被撞：相邻等级最低的梦境之种等级+2；若目标等级低于10，额外等级+1。</t>
-  </si>
-  <si>
-    <t>帮助新种子追赶等级，支持横向多种子。</t>
-  </si>
-  <si>
-    <t>银色小刀/藤蔓缠柄</t>
-  </si>
-  <si>
-    <t>蔓生罗盘</t>
-  </si>
-  <si>
-    <t>链结束：本次撞击链每命中1个梦境之种，使等级最高的梦境之种等级+1，最多+3。</t>
-  </si>
-  <si>
-    <t>把撞击链长度转化为梦种成长。</t>
-  </si>
-  <si>
-    <t>绿色罗盘/藤蔓指针</t>
-  </si>
-  <si>
-    <t>生态瓶</t>
-  </si>
-  <si>
-    <t>被撞：若背包中只有1个梦境之种，使其等级+3；否则所有梦境之种等级+1。</t>
-  </si>
-  <si>
-    <t>在单核巨树和多种子路线之间都能发挥作用。</t>
-  </si>
-  <si>
-    <t>玻璃生态瓶/瓶中小树</t>
-  </si>
-  <si>
-    <t>根网枢纽</t>
-  </si>
-  <si>
-    <t>被撞：每有1个相邻梦境之种，+5分，并使该梦境之种等级+1。</t>
-  </si>
-  <si>
-    <t>奖励密集摆放，是梦种与撞击站位的中期核心。</t>
-  </si>
-  <si>
-    <t>铜制根网节点</t>
-  </si>
-  <si>
-    <t>月冠温床</t>
-  </si>
-  <si>
-    <t>每个局内关卡第一次有梦境之种达到4x4：+60分。此后每捕梦4次，等级最高的梦境之种等级+2。</t>
-  </si>
-  <si>
-    <t>后期成型补强，奖励完成巨大梦种。</t>
-  </si>
-  <si>
-    <t>月冠形大型温床</t>
-  </si>
-  <si>
-    <t>星根祭坛</t>
-  </si>
-  <si>
-    <t>2x3</t>
-  </si>
-  <si>
-    <t>链结束：若本次撞击链命中过4x4梦境之种，+该梦境之种等级x3分。每个局内关卡限1次。</t>
-  </si>
-  <si>
-    <t>给4x4梦种一个高价值撞击终端。</t>
-  </si>
-  <si>
-    <t>星纹石祭坛/根须光路</t>
-  </si>
-  <si>
-    <t>巨木回声</t>
-  </si>
-  <si>
-    <t>每个局内关卡第一次4x4梦境之种被撞后：从该梦境之种发起一次撞击！</t>
-  </si>
-  <si>
-    <t>后期让巨大梦种从纯收益点变成撞击链节点。</t>
-  </si>
-  <si>
-    <t>树心回声纹/发光年轮</t>
-  </si>
-  <si>
-    <t>梦之种</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>机械/梦之种</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁珠</t>
-  </si>
-  <si>
-    <t>捕梦到另一枚铁珠时：撞击！</t>
-  </si>
-  <si>
-    <t>旧铁珠/轻微锈迹</t>
-  </si>
-  <si>
-    <t>小齿轮</t>
-  </si>
-  <si>
-    <t>被撞：+3分。若本次链已命中2个或以上机械物品，额外+2分。</t>
-  </si>
-  <si>
-    <t>小铜齿轮</t>
-  </si>
-  <si>
-    <t>传动皮带</t>
-  </si>
-  <si>
-    <t>被撞：+4分。若自身成功传导撞击，额外+3分。</t>
-  </si>
-  <si>
-    <t>黑色橡胶皮带</t>
-  </si>
-  <si>
-    <t>顺转弯管</t>
-  </si>
-  <si>
-    <t>机械/传动</t>
-  </si>
-  <si>
-    <t>被撞：顺转传动！每条链限1次。</t>
-  </si>
-  <si>
-    <t>L形铜管/顺时针标记</t>
-  </si>
-  <si>
-    <t>逆转弯管</t>
-  </si>
-  <si>
-    <t>被撞：逆转传动！每条链限1次。</t>
-  </si>
-  <si>
-    <t>L形铁管/逆时针标记</t>
-  </si>
-  <si>
-    <t>制动片</t>
-  </si>
-  <si>
-    <t>被撞：+8分，本条分支停止传导。</t>
-  </si>
-  <si>
-    <t>磨损刹车片</t>
-  </si>
-  <si>
-    <t>齿条</t>
-  </si>
-  <si>
-    <t>被撞：+本次链机械命中数分，最多+10分。若自身成功传导撞击，额外+4分。</t>
-  </si>
-  <si>
-    <t>长条齿轨</t>
-  </si>
-  <si>
-    <t>差速器</t>
-  </si>
-  <si>
-    <t>链结束：+本次链机械命中数x2分；若本次链转向次数大于等于2，额外+10分。</t>
-  </si>
-  <si>
-    <t>齿轮差速器</t>
-  </si>
-  <si>
-    <t>双轴转轮</t>
-  </si>
-  <si>
-    <t>被撞：若本次链机械命中数大于等于3，双向传动！每条链限1次。</t>
-  </si>
-  <si>
-    <t>双层转轮</t>
-  </si>
-  <si>
-    <t>蓄能飞轮</t>
-  </si>
-  <si>
-    <t>每当本次链累计命中3个机械物品：+12分。每条链最多触发2次。</t>
-  </si>
-  <si>
-    <t>发光飞轮</t>
-  </si>
-  <si>
-    <t>曲轴</t>
-  </si>
-  <si>
-    <t>被撞：逆转传动！若该传动命中机械物品，+10分。每条链限1次。</t>
-  </si>
-  <si>
-    <t>弯折曲轴</t>
-  </si>
-  <si>
-    <t>计数轮</t>
-  </si>
-  <si>
-    <t>链结束：若本次链命中大于等于6个物品，+18分；若大于等于9个，改为+32分。</t>
-  </si>
-  <si>
-    <t>数字计数轮</t>
-  </si>
-  <si>
-    <t>中央引擎</t>
-  </si>
-  <si>
-    <t>机械/核心</t>
-  </si>
-  <si>
-    <t>链结束：若本次链机械命中数大于等于10，+60分；若本次链转向次数大于等于3，额外+30分。</t>
-  </si>
-  <si>
-    <t>小型梦境引擎</t>
-  </si>
-  <si>
-    <t>终端计算机</t>
-  </si>
-  <si>
-    <t>链结束：+本次链机械命中数x3分，最多+45分；若本次链包含双向传动，额外+15分。</t>
-  </si>
-  <si>
-    <t>旧终端屏幕/齿轮接口</t>
-  </si>
-  <si>
-    <t>星环轴承</t>
-  </si>
-  <si>
-    <t>机械/传动/核心</t>
-  </si>
-  <si>
-    <t>每个局内关卡第一次被撞：全向传动！这些分支不能再次触发星环轴承。</t>
-  </si>
-  <si>
-    <t>星环形轴承</t>
   </si>
 </sst>
 </file>
@@ -1388,19 +1288,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
@@ -1409,10 +1309,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="6"/>
     </row>
@@ -1421,10 +1321,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D2" s="8">
         <v>-5</v>
@@ -1433,16 +1333,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="1"/>
@@ -1452,10 +1352,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8">
         <v>-5</v>
@@ -1464,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="1"/>
@@ -1483,10 +1383,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D4" s="8">
         <v>5</v>
@@ -1496,13 +1396,13 @@
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="1"/>
@@ -1512,10 +1412,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D5" s="8">
         <v>-6</v>
@@ -1524,16 +1424,16 @@
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -1549,10 +1449,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D6" s="8">
         <v>-10</v>
@@ -1561,16 +1461,16 @@
         <v>4</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -1586,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D7" s="8">
         <v>-7</v>
@@ -1598,16 +1498,16 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -1623,10 +1523,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D8" s="8">
         <v>8</v>
@@ -1636,16 +1536,16 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
@@ -1661,10 +1561,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D9" s="8">
         <v>-20</v>
@@ -1673,16 +1573,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -1698,10 +1598,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D10" s="8">
         <v>-25</v>
@@ -1710,16 +1610,16 @@
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -1735,10 +1635,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D11" s="8">
         <v>-25</v>
@@ -1747,16 +1647,16 @@
         <v>18</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -1772,10 +1672,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D12" s="8">
         <v>5</v>
@@ -1784,13 +1684,13 @@
         <v>8</v>
       </c>
       <c r="F12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I12" s="8"/>
       <c r="M12" s="8"/>
@@ -1828,10 +1728,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D14" s="8">
         <v>-25</v>
@@ -1840,16 +1740,16 @@
         <v>20</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -1865,10 +1765,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D15" s="8">
         <v>-30</v>
@@ -1877,16 +1777,16 @@
         <v>20</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
@@ -1902,10 +1802,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D16" s="8">
         <v>15</v>
@@ -1914,13 +1814,13 @@
         <v>12</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="H16" s="8" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>61</v>
@@ -1942,7 +1842,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D17" s="8">
         <v>-30</v>
@@ -1954,13 +1854,13 @@
         <v>63</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -2454,7 +2354,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BC56F0-F526-4B1D-8544-516A0AD02E1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{46BC56F0-F526-4B1D-8544-516A0AD02E1A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2464,24 +2364,24 @@
     <col min="8" max="8" width="76.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -2490,442 +2390,442 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>213</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>6</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>232</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>238</v>
+        <v>98</v>
       </c>
       <c r="I11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="F12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>243</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>244</v>
+        <v>104</v>
       </c>
       <c r="I13" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="F14">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>248</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="F15">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="F16">
         <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>255</v>
+        <v>116</v>
       </c>
       <c r="I16" t="s">
-        <v>256</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +2835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD51D4CC-8D74-4158-BD3D-2E74B32B1C81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{DD51D4CC-8D74-4158-BD3D-2E74B32B1C81}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2945,24 +2845,24 @@
     <col min="8" max="8" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -2971,149 +2871,149 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
         <v>130</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I4" t="s">
         <v>131</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J4" t="s">
         <v>132</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="C5" t="s">
         <v>134</v>
       </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
         <v>135</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I5" t="s">
         <v>136</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -3122,30 +3022,30 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I6" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -3154,30 +3054,30 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="J7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3186,30 +3086,30 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -3218,30 +3118,30 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -3250,30 +3150,30 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I10" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -3282,30 +3182,30 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I11" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D12">
         <v>12</v>
@@ -3314,30 +3214,30 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>15</v>
@@ -3346,30 +3246,30 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="G13" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I13" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>12</v>
@@ -3378,30 +3278,30 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I14" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -3410,30 +3310,30 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>18</v>
@@ -3442,30 +3342,30 @@
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I16" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J16" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>20</v>
@@ -3474,30 +3374,30 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -3506,30 +3406,30 @@
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I18" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="D19">
         <v>30</v>
@@ -3538,30 +3438,30 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="J19" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>26</v>
@@ -3570,19 +3470,19 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I20" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J20" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3611,19 +3511,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
@@ -3632,7 +3532,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -3640,25 +3540,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3666,10 +3566,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -3678,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3689,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -3701,10 +3601,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3712,10 +3612,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -3724,10 +3624,10 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3735,10 +3635,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -3747,10 +3647,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3758,10 +3658,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -3770,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3781,10 +3681,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -3793,10 +3693,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3804,25 +3704,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3830,10 +3730,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -3842,10 +3742,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3853,10 +3753,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3865,10 +3765,10 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="H11" t="s">
-        <v>93</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3876,10 +3776,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>20</v>
@@ -3888,13 +3788,13 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="H12" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4098,57 +3998,70 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0EECB-104A-4ADE-A646-4C547272FF2A}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="13.7265625" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" customWidth="1"/>
-    <col min="8" max="8" width="48.7265625" customWidth="1"/>
-    <col min="9" max="9" width="26.1796875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>物品</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>格子</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>梦值消耗</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>视觉效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小补丁</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D2">
         <v>5</v>
@@ -4156,25 +4069,40 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>目标物品本局内价值+3。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>布补丁/创可贴</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>梦值糖</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D3">
         <v>5</v>
@@ -4182,518 +4110,561 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>下一次捕梦梦值消耗-2，最低为1。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>包装糖果/月亮糖</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>转向螺丝</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>目标物品顺时针旋转一次；若旋转后仍在背包内，+2分。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>弯箭头螺丝</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>破弹珠</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D5">
         <v>8</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>从目标物品发起一次撞击！</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>裂纹弹珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>黑墨滴</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>目标物品+1污染；若目标是废弃物，额外+1污染。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>黑色墨滴</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>消毒喷雾</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D7">
         <v>8</v>
       </c>
       <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>净化目标物品全部污染；每净化1层+3分。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>喷雾瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>腐蚀酸</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>罕见道具</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>目标物品+2污染，并使其本局内价值-5。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>酸液瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小水滴</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>若目标是梦境之种，使其等级+1；若目标是空格，播种。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>发光水滴</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>肥料包</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>若目标为空格，播种；若目标是梦境之种，等级+2。</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>肥料小袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
-        <v>91</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>快速发芽剂</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>罕见道具</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>目标梦境之种等级+3；若因此变大，+8分。</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>生长药剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>延长钩</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>目标物品本局内被撞后，若没有继续传导，额外向其方向再检查1格。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>金属钩</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>传动油</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>罕见道具</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>目标机械物品本局内成功传导撞击或曲线传动命中机械物品时，额外+3分，最多触发3次。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>小油壶</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>苹果蜡</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>目标食物本局内丢弃时额外+2梦值；若目标是苹果，额外播种。</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>蜡封苹果</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>回收夹</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>罕见道具</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>下一次丢弃物品时，若它是废弃物，+8分并获得1个皱纸团。</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>金属夹</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>空白符纸</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="D16">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
-        <v>25</v>
-      </c>
-      <c r="E21">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" t="s">
-        <v>104</v>
-      </c>
-      <c r="G31" t="s">
-        <v>106</v>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>罕见道具</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>刷新目标饰品“每个局内关卡限1次”的触发次数。每个饰品每个局内关卡最多被刷新1次。</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>空白符纸</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
+++ b/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
@@ -1,34 +1,44 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4885F93-706F-48DF-8836-D6C87BAAC3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="污染" sheetId="3" r:id="rId1"/>
-    <sheet name="机械" sheetId="4" r:id="rId2"/>
-    <sheet name="梦境之种" sheetId="5" r:id="rId3"/>
-    <sheet name="通用" sheetId="6" r:id="rId4"/>
-    <sheet name="道具" sheetId="7" r:id="rId5"/>
-  </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <TotalTime>0</TotalTime>
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>5</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="5" baseType="lpstr">
+      <vt:lpstr>污染</vt:lpstr>
+      <vt:lpstr>机械</vt:lpstr>
+      <vt:lpstr>梦境之种</vt:lpstr>
+      <vt:lpstr>通用</vt:lpstr>
+      <vt:lpstr>道具</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>Isaccson August</cp:lastModifiedBy>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-05-14T06:48:51Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="232">
   <si>
     <t>序号</t>
@@ -184,15 +194,11 @@
   <si>
     <t>被撞：相邻所有废弃物+1污染</t>
   </si>
-  <si>
-    <t>隔离箱</t>
-  </si>
+  <si>污封箱</si>
   <si>
     <t>机械</t>
   </si>
-  <si>
-    <t>污染层数导致的梦值扣除效应-1</t>
-  </si>
+  <si>被撞：所指方向第一个物品污染+1；若目标已有污染，则本次撞击结算结束后相邻1格内随机1个物品污染+1。</si>
   <si>
     <t>旧足球</t>
   </si>
@@ -767,7 +773,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -974,7 +980,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1269,7 +1275,36 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4885F93-706F-48DF-8836-D6C87BAAC3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="污染" sheetId="3" r:id="rId1"/>
+    <sheet name="机械" sheetId="4" r:id="rId2"/>
+    <sheet name="梦境之种" sheetId="5" r:id="rId3"/>
+    <sheet name="通用" sheetId="6" r:id="rId4"/>
+    <sheet name="道具" sheetId="7" r:id="rId5"/>
+  </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB9B9BD-AF62-4C4D-AEE8-E856B9FC7F56}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2353,7 +2388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{46BC56F0-F526-4B1D-8544-516A0AD02E1A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2834,7 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{DD51D4CC-8D74-4158-BD3D-2E74B32B1C81}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3495,7 +3530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8133C797-C29D-4E8F-AE0A-941547D59A04}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3997,7 +4032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
+++ b/spec/Docs/01_Design/CardDesignVersion/物品列表.xlsx
@@ -1,45 +1,35 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <TotalTime>0</TotalTime>
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>5</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="5" baseType="lpstr">
-      <vt:lpstr>污染</vt:lpstr>
-      <vt:lpstr>机械</vt:lpstr>
-      <vt:lpstr>梦境之种</vt:lpstr>
-      <vt:lpstr>通用</vt:lpstr>
-      <vt:lpstr>道具</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EA5621-1FC6-4A2E-ABB7-A3A010984AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="污染" sheetId="3" r:id="rId1"/>
+    <sheet name="机械" sheetId="4" r:id="rId2"/>
+    <sheet name="梦境之种" sheetId="5" r:id="rId3"/>
+    <sheet name="通用" sheetId="6" r:id="rId4"/>
+    <sheet name="道具" sheetId="7" r:id="rId5"/>
+  </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>Isaccson August</cp:lastModifiedBy>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-05-14T06:48:51Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="232">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="277">
   <si>
     <t>序号</t>
   </si>
@@ -194,11 +184,12 @@
   <si>
     <t>被撞：相邻所有废弃物+1污染</t>
   </si>
-  <si>污封箱</si>
   <si>
     <t>机械</t>
   </si>
-  <si>被撞：所指方向第一个物品污染+1；若目标已有污染，则本次撞击结算结束后相邻1格内随机1个物品污染+1。</si>
+  <si>
+    <t/>
+  </si>
   <si>
     <t>旧足球</t>
   </si>
@@ -769,11 +760,149 @@
   <si>
     <t>当梦值归0但分数不满足要求时：回复5梦值，然后此物品消失</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>小补丁</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>目标物品本局内价值+3。</t>
+  </si>
+  <si>
+    <t>布补丁/创可贴</t>
+  </si>
+  <si>
+    <t>梦值糖</t>
+  </si>
+  <si>
+    <t>下一次捕梦梦值消耗-2，最低为1。</t>
+  </si>
+  <si>
+    <t>包装糖果/月亮糖</t>
+  </si>
+  <si>
+    <t>转向螺丝</t>
+  </si>
+  <si>
+    <t>目标物品顺时针旋转一次；若旋转后仍在背包内，+2分。</t>
+  </si>
+  <si>
+    <t>弯箭头螺丝</t>
+  </si>
+  <si>
+    <t>破弹珠</t>
+  </si>
+  <si>
+    <t>从目标物品发起一次撞击！</t>
+  </si>
+  <si>
+    <t>裂纹弹珠</t>
+  </si>
+  <si>
+    <t>黑墨滴</t>
+  </si>
+  <si>
+    <t>目标物品+1污染；若目标是废弃物，额外+1污染。</t>
+  </si>
+  <si>
+    <t>黑色墨滴</t>
+  </si>
+  <si>
+    <t>消毒喷雾</t>
+  </si>
+  <si>
+    <t>净化目标物品全部污染；每净化1层+3分。</t>
+  </si>
+  <si>
+    <t>喷雾瓶</t>
+  </si>
+  <si>
+    <t>腐蚀酸</t>
+  </si>
+  <si>
+    <t>罕见道具</t>
+  </si>
+  <si>
+    <t>目标物品+2污染，并使其本局内价值-5。</t>
+  </si>
+  <si>
+    <t>酸液瓶</t>
+  </si>
+  <si>
+    <t>小水滴</t>
+  </si>
+  <si>
+    <t>若目标是梦境之种，使其等级+1；若目标是空格，播种。</t>
+  </si>
+  <si>
+    <t>发光水滴</t>
+  </si>
+  <si>
+    <t>肥料包</t>
+  </si>
+  <si>
+    <t>若目标为空格，播种；若目标是梦境之种，等级+2。</t>
+  </si>
+  <si>
+    <t>肥料小袋</t>
+  </si>
+  <si>
+    <t>快速发芽剂</t>
+  </si>
+  <si>
+    <t>目标梦境之种等级+3；若因此变大，+8分。</t>
+  </si>
+  <si>
+    <t>生长药剂</t>
+  </si>
+  <si>
+    <t>延长钩</t>
+  </si>
+  <si>
+    <t>目标物品本局内被撞后，若没有继续传导，额外向其方向再检查1格。</t>
+  </si>
+  <si>
+    <t>金属钩</t>
+  </si>
+  <si>
+    <t>传动油</t>
+  </si>
+  <si>
+    <t>目标机械物品本局内成功传导撞击或曲线传动命中机械物品时，额外+3分，最多触发3次。</t>
+  </si>
+  <si>
+    <t>小油壶</t>
+  </si>
+  <si>
+    <t>苹果蜡</t>
+  </si>
+  <si>
+    <t>目标食物本局内丢弃时额外+2梦值；若目标是苹果，额外播种。</t>
+  </si>
+  <si>
+    <t>蜡封苹果</t>
+  </si>
+  <si>
+    <t>回收夹</t>
+  </si>
+  <si>
+    <t>下一次丢弃物品时，若它是废弃物，+8分并获得1个皱纸团。</t>
+  </si>
+  <si>
+    <t>金属夹</t>
+  </si>
+  <si>
+    <t>空白符纸</t>
+  </si>
+  <si>
+    <t>刷新目标饰品“每个局内关卡限1次”的触发次数。每个饰品每个局内关卡最多被刷新1次。</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -980,7 +1109,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1275,36 +1404,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\GodotProjects\Lost-Fragments\spec\Docs\01_Design\CardDesignVersion\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4885F93-706F-48DF-8836-D6C87BAAC3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="污染" sheetId="3" r:id="rId1"/>
-    <sheet name="机械" sheetId="4" r:id="rId2"/>
-    <sheet name="梦境之种" sheetId="5" r:id="rId3"/>
-    <sheet name="通用" sheetId="6" r:id="rId4"/>
-    <sheet name="道具" sheetId="7" r:id="rId5"/>
-  </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB9B9BD-AF62-4C4D-AEE8-E856B9FC7F56}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1702,30 +1802,18 @@
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
     </row>
-    <row r="12" spans="1:20" ht="31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="8">
-        <v>5</v>
-      </c>
-      <c r="E12" s="8">
-        <v>8</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="8"/>
       <c r="M12" s="8"/>
@@ -1763,7 +1851,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>28</v>
@@ -1781,10 +1869,10 @@
         <v>13</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -1800,7 +1888,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>28</v>
@@ -1818,10 +1906,10 @@
         <v>13</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
@@ -1837,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>48</v>
@@ -1849,16 +1937,16 @@
         <v>12</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -1874,7 +1962,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>11</v>
@@ -1886,16 +1974,16 @@
         <v>20</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -2388,8 +2476,8 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{46BC56F0-F526-4B1D-8544-516A0AD02E1A}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BC56F0-F526-4B1D-8544-516A0AD02E1A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2399,24 +2487,24 @@
     <col min="8" max="8" width="76.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
         <v>65</v>
-      </c>
-      <c r="C1" t="s">
-        <v>66</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
         <v>67</v>
-      </c>
-      <c r="F1" t="s">
-        <v>68</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -2428,12 +2516,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -2442,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2451,18 +2539,18 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
         <v>70</v>
       </c>
-      <c r="I2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -2471,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2480,18 +2568,18 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" t="s">
         <v>73</v>
       </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -2500,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -2509,18 +2597,18 @@
         <v>24</v>
       </c>
       <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" t="s">
         <v>76</v>
       </c>
-      <c r="I4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -2529,7 +2617,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -2538,18 +2626,18 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -2558,7 +2646,7 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -2567,18 +2655,18 @@
         <v>40</v>
       </c>
       <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" t="s">
         <v>83</v>
       </c>
-      <c r="I6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -2587,7 +2675,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -2596,18 +2684,18 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" t="s">
         <v>86</v>
       </c>
-      <c r="I7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -2616,7 +2704,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2625,18 +2713,18 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" t="s">
         <v>89</v>
       </c>
-      <c r="I8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -2645,7 +2733,7 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -2654,18 +2742,18 @@
         <v>13</v>
       </c>
       <c r="H9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" t="s">
         <v>92</v>
       </c>
-      <c r="I9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -2674,7 +2762,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -2683,18 +2771,18 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" t="s">
         <v>95</v>
       </c>
-      <c r="I10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -2703,7 +2791,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -2712,18 +2800,18 @@
         <v>13</v>
       </c>
       <c r="H11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" t="s">
         <v>98</v>
       </c>
-      <c r="I11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2732,7 +2820,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -2741,18 +2829,18 @@
         <v>24</v>
       </c>
       <c r="H12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
         <v>101</v>
       </c>
-      <c r="I12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -2761,7 +2849,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -2770,18 +2858,18 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" t="s">
         <v>104</v>
       </c>
-      <c r="I13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
@@ -2790,7 +2878,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F14">
         <v>14</v>
@@ -2799,27 +2887,27 @@
         <v>13</v>
       </c>
       <c r="H14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
         <v>110</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15">
         <v>16</v>
@@ -2828,18 +2916,18 @@
         <v>24</v>
       </c>
       <c r="H15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" t="s">
         <v>112</v>
       </c>
-      <c r="I15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -2848,7 +2936,7 @@
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16">
         <v>18</v>
@@ -2857,10 +2945,10 @@
         <v>13</v>
       </c>
       <c r="H16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" t="s">
         <v>116</v>
-      </c>
-      <c r="I16" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2869,8 +2957,8 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{DD51D4CC-8D74-4158-BD3D-2E74B32B1C81}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD51D4CC-8D74-4158-BD3D-2E74B32B1C81}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2880,7 +2968,7 @@
     <col min="8" max="8" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2912,140 +3000,140 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>118</v>
+      <c r="B2" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" t="s">
         <v>119</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>120</v>
-      </c>
-      <c r="F2" t="s">
-        <v>121</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
       <c r="H2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" t="s">
         <v>122</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>123</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" t="s">
         <v>119</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>120</v>
-      </c>
-      <c r="F3" t="s">
-        <v>121</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" t="s">
         <v>126</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>127</v>
       </c>
-      <c r="J3" t="s">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
         <v>119</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>120</v>
-      </c>
-      <c r="F4" t="s">
-        <v>121</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" t="s">
         <v>130</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>131</v>
       </c>
-      <c r="J4" t="s">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>133</v>
       </c>
-      <c r="C5" t="s">
-        <v>134</v>
-      </c>
       <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
         <v>119</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>120</v>
-      </c>
-      <c r="F5" t="s">
-        <v>121</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
       </c>
       <c r="H5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" t="s">
         <v>135</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>136</v>
       </c>
-      <c r="J5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -3057,27 +3145,27 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" t="s">
         <v>139</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>140</v>
       </c>
-      <c r="J6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -3089,27 +3177,27 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" t="s">
         <v>143</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>144</v>
       </c>
-      <c r="J7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -3121,27 +3209,27 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" t="s">
         <v>147</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>148</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>149</v>
       </c>
-      <c r="J8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -3153,27 +3241,27 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" t="s">
         <v>152</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>153</v>
       </c>
-      <c r="J9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -3185,27 +3273,27 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
       </c>
       <c r="H10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" t="s">
         <v>156</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>157</v>
       </c>
-      <c r="J10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -3217,27 +3305,27 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" t="s">
         <v>40</v>
       </c>
       <c r="H11" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" t="s">
         <v>160</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>161</v>
       </c>
-      <c r="J11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
@@ -3249,27 +3337,27 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G12" t="s">
         <v>24</v>
       </c>
       <c r="H12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" t="s">
         <v>165</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>166</v>
       </c>
-      <c r="J12" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -3281,27 +3369,27 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" t="s">
         <v>169</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>170</v>
       </c>
-      <c r="J13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -3313,27 +3401,27 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
         <v>40</v>
       </c>
       <c r="H14" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" t="s">
         <v>173</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>174</v>
       </c>
-      <c r="J14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -3345,27 +3433,27 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I15" t="s">
         <v>177</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>178</v>
       </c>
-      <c r="J15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -3377,27 +3465,27 @@
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" t="s">
         <v>181</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>182</v>
       </c>
-      <c r="J16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
@@ -3409,27 +3497,27 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" t="s">
         <v>185</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>186</v>
       </c>
-      <c r="J17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s">
         <v>48</v>
@@ -3441,30 +3529,30 @@
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18" t="s">
+        <v>188</v>
+      </c>
+      <c r="I18" t="s">
         <v>189</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>190</v>
       </c>
-      <c r="J18" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19">
         <v>30</v>
@@ -3473,27 +3561,27 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
       </c>
       <c r="H19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I19" t="s">
         <v>193</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>194</v>
       </c>
-      <c r="J19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -3505,19 +3593,19 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20" t="s">
+        <v>196</v>
+      </c>
+      <c r="I20" t="s">
         <v>197</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>198</v>
-      </c>
-      <c r="J20" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3530,7 +3618,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8133C797-C29D-4E8F-AE0A-941547D59A04}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3575,25 +3663,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3601,10 +3689,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -3613,10 +3701,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3624,10 +3712,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -3636,10 +3724,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3647,10 +3735,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" t="s">
         <v>209</v>
-      </c>
-      <c r="C5" t="s">
-        <v>210</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -3659,10 +3747,10 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H5" t="s">
         <v>211</v>
-      </c>
-      <c r="H5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3670,10 +3758,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -3682,10 +3770,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3693,10 +3781,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -3705,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" t="s">
         <v>216</v>
-      </c>
-      <c r="H7" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3716,10 +3804,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -3728,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3739,25 +3827,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" t="s">
         <v>221</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" t="s">
         <v>222</v>
-      </c>
-      <c r="G9" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3765,10 +3853,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" t="s">
         <v>224</v>
-      </c>
-      <c r="C10" t="s">
-        <v>225</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -3777,10 +3865,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3788,10 +3876,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3800,10 +3888,10 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3811,10 +3899,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D12">
         <v>20</v>
@@ -3823,13 +3911,13 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
+        <v>229</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" t="s">
         <v>230</v>
-      </c>
-      <c r="G12" t="s">
-        <v>147</v>
-      </c>
-      <c r="H12" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4032,71 +4120,49 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>物品</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>格子</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>价值</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>梦值消耗</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>标签</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>视觉效果</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>小补丁</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -4104,40 +4170,28 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>目标物品本局内价值+3。</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>布补丁/创可贴</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>梦值糖</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -4145,40 +4199,28 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>下一次捕梦梦值消耗-2，最低为1。</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>包装糖果/月亮糖</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="F3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>转向螺丝</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -4186,40 +4228,28 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>目标物品顺时针旋转一次；若旋转后仍在背包内，+2分。</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>弯箭头螺丝</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>破弹珠</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -4227,40 +4257,28 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>从目标物品发起一次撞击！</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>裂纹弹珠</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>黑墨滴</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -4268,40 +4286,28 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>目标物品+1污染；若目标是废弃物，额外+1污染。</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>黑色墨滴</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="F6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>消毒喷雾</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -4309,40 +4315,28 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>净化目标物品全部污染；每净化1层+3分。</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>喷雾瓶</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="F7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>腐蚀酸</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -4350,40 +4344,28 @@
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>罕见道具</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>目标物品+2污染，并使其本局内价值-5。</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>酸液瓶</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小水滴</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -4391,40 +4373,28 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>若目标是梦境之种，使其等级+1；若目标是空格，播种。</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>发光水滴</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>肥料包</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -4432,40 +4402,28 @@
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>若目标为空格，播种；若目标是梦境之种，等级+2。</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>肥料小袋</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>快速发芽剂</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
       </c>
       <c r="D11">
         <v>14</v>
@@ -4473,40 +4431,28 @@
       <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>罕见道具</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>目标梦境之种等级+3；若因此变大，+8分。</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>生长药剂</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" t="s">
+        <v>261</v>
+      </c>
+      <c r="I11" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>延长钩</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -4514,40 +4460,28 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>目标物品本局内被撞后，若没有继续传导，额外向其方向再检查1格。</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>金属钩</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" t="s">
+        <v>264</v>
+      </c>
+      <c r="I12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>传动油</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -4555,40 +4489,28 @@
       <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>罕见道具</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>目标机械物品本局内成功传导撞击或曲线传动命中机械物品时，额外+3分，最多触发3次。</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>小油壶</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G13" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" t="s">
+        <v>267</v>
+      </c>
+      <c r="I13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>苹果蜡</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -4596,40 +4518,28 @@
       <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>目标食物本局内丢弃时额外+2梦值；若目标是苹果，额外播种。</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>蜡封苹果</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="F14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" t="s">
+        <v>270</v>
+      </c>
+      <c r="I14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>回收夹</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
       </c>
       <c r="D15">
         <v>12</v>
@@ -4637,40 +4547,28 @@
       <c r="E15">
         <v>3</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>罕见道具</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>下一次丢弃物品时，若它是废弃物，+8分并获得1个皱纸团。</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>金属夹</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="F15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
+        <v>273</v>
+      </c>
+      <c r="I15" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>空白符纸</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
       </c>
       <c r="D16">
         <v>18</v>
@@ -4678,28 +4576,21 @@
       <c r="E16">
         <v>3</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>罕见道具</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>刷新目标饰品“每个局内关卡限1次”的触发次数。每个饰品每个局内关卡最多被刷新1次。</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>空白符纸</t>
-        </is>
+      <c r="F16" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I16" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>